--- a/src/Excelsior.Tests/TemplateSheetTests.ProtectedTemplate.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.ProtectedTemplate.verified.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookProtection workbookPassword="DAA7" lockStructure="1" lockWindows="0"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -72,4 +72,13 @@
   <sheetProtection password="DAA7" sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" sort="0" autoFilter="0" pivotTables="1" selectUnlockedCells="0"/>
   <autoFilter ref="A1:B1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Employees">
+    <column index="1" property="Name"/>
+    <column index="2" property="EmployeeId"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/TemplateSheetTests.ProtectedTemplate.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.ProtectedTemplate.verified.xlsx
@@ -69,7 +69,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="DAA7" sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" sort="0" autoFilter="0" pivotTables="1" selectUnlockedCells="0"/>
+  <sheetProtection password="DAA7" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" sort="0" autoFilter="0" pivotTables="1" selectUnlockedCells="0"/>
   <autoFilter ref="A1:B1"/>
 </worksheet>
 </file>
